--- a/sources/quranenc.com/xlsx_output/chinese_suliman.xlsx
+++ b/sources/quranenc.com/xlsx_output/chinese_suliman.xlsx
@@ -503,12 +503,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Surah</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ayah</t>
+          <t>Aya</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
